--- a/epics/1118/samples/multi_sheet/1118_data.xlsx
+++ b/epics/1118/samples/multi_sheet/1118_data.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PROJECT_SHEET" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CALENDAR_SHEET" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PROJECT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CALENDAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,12 +621,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
